--- a/sales_report.xlsx
+++ b/sales_report.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sales Report" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sales Report'!$A$1:$E$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sales Report'!$A$2:$E$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21,13 +21,17 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0.00"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="18"/>
     </font>
     <font>
       <b val="1"/>
@@ -53,12 +57,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
@@ -427,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -437,71 +444,56 @@
     <col width="15" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>SALES SUMMARY REPORT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
           <t>Customer</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Unit Price</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Total Sales</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Rahim</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Laptop</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D2" t="n">
-        <v>750</v>
-      </c>
-      <c r="E2">
-        <f>C2*D2</f>
-        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Karim</t>
+          <t>Rahim</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mouse</t>
+          <t>Laptop</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>750</v>
       </c>
       <c r="E3">
         <f>C3*D3</f>
@@ -511,19 +503,19 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sakib</t>
+          <t>Karim</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Keyboard</t>
+          <t>Mouse</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="E4">
         <f>C4*D4</f>
@@ -533,19 +525,19 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Nadia</t>
+          <t>Sakib</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Keyboard</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>220</v>
+        <v>45</v>
       </c>
       <c r="E5">
         <f>C5*D5</f>
@@ -555,19 +547,19 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Hasan</t>
+          <t>Nadia</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Headset</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>35</v>
+        <v>220</v>
       </c>
       <c r="E6">
         <f>C6*D6</f>
@@ -577,19 +569,19 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Rima</t>
+          <t>Hasan</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Webcam</t>
+          <t>Headset</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="E7">
         <f>C7*D7</f>
@@ -599,19 +591,19 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Tanvir</t>
+          <t>Rima</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Keyboard</t>
+          <t>Webcam</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="E8">
         <f>C8*D8</f>
@@ -621,74 +613,103 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Jannat</t>
+          <t>Tanvir</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mouse</t>
+          <t>Keyboard</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="E9">
         <f>C9*D9</f>
         <v/>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Jannat</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Mouse</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>20</v>
+      </c>
+      <c r="E10">
+        <f>C10*D10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Sales Summary</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Total Revenue</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
-        <v>2720</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="B13" s="4">
+        <f>SUM(E3:E10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Average Sales</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="B14" s="4">
+        <f>AVERAGE(E3:E10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Highest Sale</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="B15" s="4">
+        <f>MAX(E3:E10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Lowest Sale</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
-        <v>60</v>
+      <c r="B16" s="4">
+        <f>MIN(E3:E10)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E9"/>
+  <autoFilter ref="A2:E10"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>